--- a/data-modeling/TMDB.xlsx
+++ b/data-modeling/TMDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevPrograms\ktds-28-java-database\data-modeling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F137D1-57ED-41E4-A9F0-A73568AA4E84}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEFBC9F-8FAF-4AAC-8905-97CEC777D7C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7935" tabRatio="856" xr2:uid="{85814601-ADB8-44F5-A593-21D827287134}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7935" tabRatio="856" activeTab="2" xr2:uid="{85814601-ADB8-44F5-A593-21D827287134}"/>
   </bookViews>
   <sheets>
     <sheet name="데이터 검증-영화" sheetId="2" r:id="rId1"/>
@@ -49,16 +49,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026/07/29 (KR)</t>
-  </si>
-  <si>
     <t>개요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4년 전 소중한 사람들을 지키기 위해 모두의 기억에서 사라진 피터 파커. 친절한 이웃 스파이더맨으로서 뉴욕을 지키며 고독한 삶을 살아가던 피터는 어느 날, 예상치 못한 DNA 변이로 인해 통제 불가능한 힘에 사로잡히고 그의 진짜 정체를 알고 있는 적까지 마주하게 된다. 타인의 의식을 조종하는 정체불명의 존재로 인해 모두가 피터를 노리는 적이 될 수 있는 혼란 속에서 피터는 다시 위협에 빠진 MJ와 모두를 지키기 위해 스파이더맨으로 그들 앞에 서게 되는데...</t>
-  </si>
-  <si>
     <t>데스틴 대니얼 크레턴</t>
   </si>
   <si>
@@ -89,18 +83,12 @@
     <t>https://www.facebook.com/SpiderManMovie</t>
   </si>
   <si>
-    <t>https://x.com/SpiderManMovie</t>
-  </si>
-  <si>
     <t>https://instagram.com/spidermanmovie/</t>
   </si>
   <si>
     <t>https://spidermanbrandnewday.movie/</t>
   </si>
   <si>
-    <t>스파이더맨의 새로운 날을 확인하라!</t>
-  </si>
-  <si>
     <t>한 줄 설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -113,9 +101,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Spider-Man: Brand New Day</t>
-  </si>
-  <si>
     <t>메인 포스터</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,9 +141,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>969681-spider-man-brand-new-day</t>
-  </si>
-  <si>
     <t>제목</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,15 +165,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>878-science-fiction</t>
-  </si>
-  <si>
-    <t>28-action</t>
-  </si>
-  <si>
-    <t>12-adventure</t>
-  </si>
-  <si>
     <t>러닝 타임</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -613,14 +586,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>28-action</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>28-action</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>9648-mystery</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -766,14 +731,6 @@
   </si>
   <si>
     <t>14-fantasy</t>
-  </si>
-  <si>
-    <t>12-adventure</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12-adventure</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>14-fantasy</t>
@@ -1399,6 +1356,54 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>2026/07/29 (KR)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4년 전 소중한 사람들을 지키기 위해 모두의 기억에서 사라진 피터 파커. 친절한 이웃 스파이더맨으로서 뉴욕을 지키며 고독한 삶을 살아가던 피터는 어느 날, 예상치 못한 DNA 변이로 인해 통제 불가능한 힘에 사로잡히고 그의 진짜 정체를 알고 있는 적까지 마주하게 된다. 타인의 의식을 조종하는 정체불명의 존재로 인해 모두가 피터를 노리는 적이 될 수 있는 혼란 속에서 피터는 다시 위협에 빠진 MJ와 모두를 지키기 위해 스파이더맨으로 그들 앞에 서게 되는데...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/SpiderManMovie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://x.com/SpiderManMovie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://instagram.com/spidermanmovie/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스파이더맨의 새로운 날을 확인하라!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spider-Man: Brand New Day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-spider-man-brand-new-day</t>
+  </si>
+  <si>
+    <t>1-science-fiction</t>
+  </si>
+  <si>
+    <t>2-action</t>
+  </si>
+  <si>
+    <t>3-adventure</t>
+  </si>
+  <si>
+    <t>2-action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-adventure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1408,7 +1413,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1473,19 +1478,22 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1497,11 +1505,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1542,19 +1553,20 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -9601,8 +9613,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB11680-CC3C-4239-900E-DAE1CDBDF6B4}">
-  <dimension ref="A1:Q24"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.5" style="6" bestFit="1" customWidth="1"/>
@@ -9622,119 +9634,119 @@
     <col min="18" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B1" s="6" t="str">
-        <f>COUNTA(A4:A24)&amp;"개 Row 생성됨"</f>
-        <v>21개 Row 생성됨</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+        <f>COUNTA(A4:A13)&amp;"개 Row 생성됨"</f>
+        <v>10개 Row 생성됨</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B2" s="6" t="str">
         <f>COUNTA(3:3)&amp;"개 Column 생성됨"</f>
         <v>17개 Column 생성됨</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="L3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="P3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C4" s="5">
         <v>12</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>5</v>
+        <v>367</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="L4" s="6" t="s">
-        <v>17</v>
+        <v>371</v>
       </c>
       <c r="M4" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="P4" s="7">
         <v>225000000</v>
@@ -9743,48 +9755,48 @@
         <v>2219901026</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C5" s="6">
         <v>15</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="O5" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="P5" s="8">
         <v>18000000</v>
@@ -9793,48 +9805,48 @@
         <v>62207464</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C6" s="6">
         <v>12</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="P6" s="9">
         <v>200000000</v>
@@ -9843,45 +9855,45 @@
         <v>1921426073</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>727340</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C7" s="6">
         <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="P7" s="9">
         <v>17000000</v>
@@ -9890,48 +9902,48 @@
         <v>25994</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C8" s="6">
         <v>15</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="P8" s="11">
         <v>250000000</v>
@@ -9940,48 +9952,48 @@
         <v>1446194550</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="P9" s="9">
         <v>250000000</v>
@@ -9990,39 +10002,39 @@
         <v>1128578473</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="P10" s="9">
         <v>250000000</v>
@@ -10031,48 +10043,48 @@
         <v>308159595</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="P11" s="9">
         <v>85000000</v>
@@ -10081,80 +10093,80 @@
         <v>505515960</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1375646</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="C12" s="6">
         <v>15</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="K12" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="B13" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>348</v>
       </c>
       <c r="C13" s="6">
         <v>15</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="P13" s="9">
         <v>10000000</v>
@@ -10163,483 +10175,343 @@
         <v>395123969</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="13">
-        <f>MAX(A15:A24)</f>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <f>LEN(A4)</f>
+        <v>26</v>
+      </c>
+      <c r="B16" s="6">
+        <f t="shared" ref="B16:Q25" si="0">LEN(B4)</f>
+        <v>15</v>
+      </c>
+      <c r="C16" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D16" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" si="0"/>
+        <v>258</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H16" s="6">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="J16" s="6">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="K16" s="6">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="L16" s="6">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="M16" s="6">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="N16" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O16" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="P16" s="6">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="Q16" s="6">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <f t="shared" ref="A17:P38" si="1">LEN(A5)</f>
         <v>36</v>
       </c>
-      <c r="B14" s="13">
-        <f>MAX(B15:B24)</f>
-        <v>15</v>
-      </c>
-      <c r="C14" s="13">
-        <f>MAX(C15:C24)</f>
-        <v>3</v>
-      </c>
-      <c r="D14" s="13">
-        <f>MAX(D15:D24)</f>
-        <v>6</v>
-      </c>
-      <c r="E14" s="13">
-        <f>MAX(E15:E24)</f>
-        <v>288</v>
-      </c>
-      <c r="F14" s="13">
-        <f>MAX(F15:F24)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="13">
-        <f>MAX(G15:G24)</f>
-        <v>15</v>
-      </c>
-      <c r="H14" s="13">
-        <f>MAX(H15:H24)</f>
-        <v>42</v>
-      </c>
-      <c r="I14" s="13">
-        <f>MAX(I15:I24)</f>
-        <v>28</v>
-      </c>
-      <c r="J14" s="13">
-        <f>MAX(J15:J24)</f>
-        <v>38</v>
-      </c>
-      <c r="K14" s="13">
-        <f>MAX(K15:K24)</f>
-        <v>54</v>
-      </c>
-      <c r="L14" s="13">
-        <f>MAX(L15:L24)</f>
-        <v>19</v>
-      </c>
-      <c r="M14" s="13">
-        <f>MAX(M15:M24)</f>
-        <v>29</v>
-      </c>
-      <c r="N14" s="13">
-        <f>MAX(N15:N24)</f>
-        <v>3</v>
-      </c>
-      <c r="O14" s="13">
-        <f>MAX(O15:O24)</f>
-        <v>3</v>
-      </c>
-      <c r="P14" s="13">
-        <f>MAX(P15:P24)</f>
-        <v>9</v>
-      </c>
-      <c r="Q14" s="13">
-        <f>MAX(Q15:Q24)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15" s="6">
-        <f>LEN(A4)</f>
-        <v>31</v>
-      </c>
-      <c r="B15" s="6">
-        <f t="shared" ref="B15:Q24" si="0">LEN(B4)</f>
-        <v>15</v>
-      </c>
-      <c r="C15" s="6">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D15" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E15" s="6">
-        <f t="shared" si="0"/>
-        <v>258</v>
-      </c>
-      <c r="F15" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="H15" s="6">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="I15" s="6">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="J15" s="6">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="K15" s="6">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="L15" s="6">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="M15" s="6">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="N15" s="6">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="O15" s="6">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="P15" s="6">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Q15" s="6">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="6">
-        <f t="shared" ref="A16:P24" si="1">LEN(A5)</f>
-        <v>36</v>
-      </c>
-      <c r="B16" s="6">
+      <c r="B17" s="6">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C17" s="6">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D17" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E17" s="6">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F17" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G17" s="6">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H17" s="6">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I17" s="6">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J17" s="6">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K17" s="6">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L17" s="6">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M17" s="6">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N17" s="6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O16" s="6">
+      <c r="O17" s="6">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P17" s="6">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="Q17" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="6">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B18" s="6">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D18" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E18" s="6">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F18" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G18" s="6">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H18" s="6">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I18" s="6">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J18" s="6">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K18" s="6">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L18" s="6">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M18" s="6">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N18" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="O17" s="6">
+      <c r="O18" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P18" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q18" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="6">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B19" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C19" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D19" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E19" s="6">
         <f t="shared" si="0"/>
         <v>273</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F19" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G19" s="6">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H19" s="6">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I19" s="6">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J19" s="6">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K19" s="6">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L19" s="6">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M19" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N19" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="O18" s="6">
+      <c r="O19" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P19" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="Q19" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
-      <c r="A19" s="6">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="B19" s="6">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C19" s="6">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D19" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E19" s="6">
-        <f t="shared" si="0"/>
-        <v>185</v>
-      </c>
-      <c r="F19" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="6">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="H19" s="6">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="I19" s="6">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="J19" s="6">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="K19" s="6">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="L19" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="M19" s="6">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="N19" s="6">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="O19" s="6">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="P19" s="6">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="Q19" s="6">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B20" s="6">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C20" s="6">
         <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D20" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H20" s="6">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="K20" s="6">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="M20" s="6">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="N20" s="6">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D20" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E20" s="6">
-        <f t="shared" si="0"/>
-        <v>288</v>
-      </c>
-      <c r="F20" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="6">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="H20" s="6">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="I20" s="6">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="J20" s="6">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="K20" s="6">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="L20" s="6">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="M20" s="6">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="N20" s="6">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
       <c r="O20" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -10653,282 +10525,352 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B21" s="6">
         <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C21" s="6">
+      <c r="D21" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" si="0"/>
+        <v>288</v>
+      </c>
+      <c r="F21" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H21" s="6">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="J21" s="6">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="K21" s="6">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="L21" s="6">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="M21" s="6">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="N21" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O21" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D21" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E21" s="6">
-        <f t="shared" si="0"/>
-        <v>178</v>
-      </c>
-      <c r="F21" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="6">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="H21" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="6">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="L21" s="6">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="M21" s="6">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N21" s="6">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="O21" s="6">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
       <c r="P21" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B22" s="6">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C22" s="6">
         <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D22" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E22" s="6">
+        <f t="shared" si="0"/>
+        <v>178</v>
+      </c>
+      <c r="F22" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H22" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="6">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="L22" s="6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="M22" s="6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="N22" s="6">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D22" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E22" s="6">
-        <f t="shared" si="0"/>
-        <v>157</v>
-      </c>
-      <c r="F22" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="6">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="H22" s="6">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="I22" s="6">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="J22" s="6">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="K22" s="6">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="L22" s="6">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="M22" s="6">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="N22" s="6">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
       <c r="O22" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B23" s="6">
         <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D23" s="6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="shared" si="0"/>
+        <v>157</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H23" s="6">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="K23" s="6">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="L23" s="6">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M23" s="6">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="N23" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O23" s="6">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D23" s="6">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E23" s="6">
-        <f t="shared" si="0"/>
-        <v>278</v>
-      </c>
-      <c r="F23" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="H23" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="L23" s="6">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="M23" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="6">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="O23" s="6">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
       <c r="P23" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B24" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D24" s="6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E24" s="6">
+        <f t="shared" si="0"/>
+        <v>278</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="6">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="L24" s="6">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O24" s="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="6">
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B25" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C25" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D25" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E25" s="6">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F25" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G25" s="6">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H25" s="6">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I25" s="6">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J25" s="6">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K25" s="6">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L25" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M25" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N25" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="O24" s="6">
+      <c r="O25" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P25" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="Q25" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -10940,97 +10882,102 @@
       <formula>NOT(ISERROR(SEARCH("~",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="H4" r:id="rId1" xr:uid="{8223DE56-083C-4B0B-8411-DD27906CBF04}"/>
+    <hyperlink ref="I4" r:id="rId2" xr:uid="{34AA2CAA-2927-4891-9129-EE62534D2B00}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{6C1B84F7-69FD-4FE2-872E-50ADE1ECD896}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75B5E3F-FCB4-447E-A68F-699EA6FF3466}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -11038,7 +10985,7 @@
         <v>727340</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -11046,115 +10993,115 @@
         <v>727340</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>A11+1</f>
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" ref="A13:A29" si="0">A12+1</f>
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -11163,7 +11110,7 @@
         <v>1375646</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -11172,7 +11119,7 @@
         <v>1375646</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -11181,31 +11128,31 @@
         <v>1375646</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -11218,88 +11165,88 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E98A32-B05C-4AB0-AE12-57B5147827AF}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -11307,7 +11254,7 @@
         <v>727340</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -11315,115 +11262,115 @@
         <v>727340</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f>A11+1</f>
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" ref="A13:A29" si="0">A12+1</f>
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -11432,7 +11379,7 @@
         <v>1375646</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -11441,7 +11388,7 @@
         <v>1375646</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -11450,31 +11397,31 @@
         <v>1375646</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -11487,106 +11434,107 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2DBBCD-EBED-4648-907F-562BA4A4FE2D}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="6"/>
+    <col min="2" max="2" width="11" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>374</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>163</v>
+        <v>375</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>205</v>
+        <v>376</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -11598,7 +11546,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CA507F-FD73-43D0-8E7A-96D69324C546}">
   <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.375" style="2" bestFit="1" customWidth="1"/>
@@ -11606,378 +11554,378 @@
     <col min="4" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>374</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>374</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>377</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>375</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>378</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>376</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>164</v>
+        <v>375</v>
       </c>
       <c r="C10" s="2">
         <v>727340</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C11" s="2">
         <v>727340</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2">
         <v>727340</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>206</v>
+        <v>376</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>375</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>41</v>
+        <v>376</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>376</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>41</v>
+        <v>376</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>39</v>
+        <v>374</v>
       </c>
       <c r="C29" s="2">
         <v>1375646</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>40</v>
+        <v>375</v>
       </c>
       <c r="C30" s="2">
         <v>1375646</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="C31" s="2">
         <v>1375646</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>39</v>
+        <v>374</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -11989,7 +11937,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C030775-0B4B-4EFB-A546-32641B0FABC0}">
   <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.75" style="6" bestFit="1" customWidth="1"/>
@@ -11997,437 +11945,437 @@
     <col min="4" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>73249</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>17120</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>150126</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-    </row>
-    <row r="24" spans="1:5">
+        <v>158</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>939147</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>2725917</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>63436</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>1096458</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>1253391</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -12460,7 +12408,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EF2A93-2BAB-4345-A329-4A445ABEA7C6}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.25" style="2" bestFit="1" customWidth="1"/>
@@ -12469,296 +12417,296 @@
     <col min="5" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C17" s="2">
         <v>727340</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -12769,13 +12717,13 @@
         <v>727340</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -12786,251 +12734,251 @@
         <v>727340</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -13041,13 +12989,13 @@
         <v>1375646</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -13058,13 +13006,13 @@
         <v>1375646</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -13075,44 +13023,44 @@
         <v>1375646</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -13124,7 +13072,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49C4F54-B53C-4899-938D-C2AC0541D34C}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.75" style="2" bestFit="1" customWidth="1"/>
@@ -13133,189 +13081,189 @@
     <col min="5" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -13326,10 +13274,10 @@
         <v>727340</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -13340,10 +13288,10 @@
         <v>727340</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -13354,178 +13302,178 @@
         <v>727340</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -13536,10 +13484,10 @@
         <v>1375646</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -13550,10 +13498,10 @@
         <v>1375646</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -13564,49 +13512,49 @@
         <v>1375646</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -13618,235 +13566,235 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91CFBB52-746C-4430-B733-87644DA2F926}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.75" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -13858,124 +13806,124 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB2AAC24-A560-4C2C-B2CE-80CA1A9B5E59}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.75" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>373</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -13983,10 +13931,10 @@
         <v>727340</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -13994,10 +13942,10 @@
         <v>727340</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -14005,142 +13953,142 @@
         <v>727340</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -14148,40 +14096,40 @@
         <v>1375646</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -14193,80 +14141,80 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AD15F0C-A40C-4E06-8007-81D787B10803}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
     <col min="3" max="3" width="35.875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -14275,7 +14223,7 @@
         <v>727340</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -14283,115 +14231,115 @@
         <v>727340</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" ref="A11:A18" si="0">+A10+1</f>
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" ref="A19:A28" si="1">+A18+1</f>
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -14400,7 +14348,7 @@
         <v>1375646</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -14409,7 +14357,7 @@
         <v>1375646</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -14418,31 +14366,31 @@
         <v>1375646</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
